--- a/task124/golden/lslr_2027_programme.xlsx
+++ b/task124/golden/lslr_2027_programme.xlsx
@@ -22,9 +22,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="68">
-  <si>
-    <t>Every zone finished by 2037 at $27.1 million a year: lead service line replacement schedule, 2027 to 2037</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="75">
+  <si>
+    <t>Every zone finished by 2037 at $25.4 million a year: lead service line replacement schedule, 2027 to 2037</t>
   </si>
   <si>
     <t>Hollins Ford Regional Water District, LSLR programme office. Plan revision 2 zones in priority order; plan cost in 2027 dollars at the 2027 unit cost schedule. Prepared 11 January 2027 for the board meeting of 19 January 2027.</t>
@@ -96,79 +96,100 @@
     <t>Depot Square</t>
   </si>
   <si>
+    <t>RZ-03</t>
+  </si>
+  <si>
+    <t>Millrace</t>
+  </si>
+  <si>
     <t>RZ-12</t>
   </si>
   <si>
     <t>Kittering Village</t>
   </si>
   <si>
-    <t>RZ-03</t>
-  </si>
-  <si>
-    <t>Millrace</t>
-  </si>
-  <si>
     <t>RZ-08</t>
   </si>
   <si>
     <t>Elm Park</t>
   </si>
   <si>
+    <t>RZ-06</t>
+  </si>
+  <si>
+    <t>Wexley</t>
+  </si>
+  <si>
     <t>RZ-10</t>
   </si>
   <si>
     <t>Lakeview Terrace</t>
   </si>
   <si>
-    <t>RZ-06</t>
-  </si>
-  <si>
-    <t>Wexley</t>
-  </si>
-  <si>
     <t>All twelve zones</t>
   </si>
   <si>
-    <t>Last zone: RZ-06 Wexley, finished in programme year 2037, inside the 1 November 2037 deadline.</t>
-  </si>
-  <si>
-    <t>Lines to replace: the zone's Lead and GRR lines plus its Lead Status Unknown lines at the share found lead or GRR in their construction era on the segments verified whole (sheet Unknown-line shares).</t>
+    <t>Last zone: RZ-10 Lakeview Terrace, finished in programme year 2037, inside the 1 November 2037 deadline.</t>
+  </si>
+  <si>
+    <t>Lines to replace: the zone's Lead and GRR lines plus its Lead Status Unknown lines at the share of lead or GRR expected among the district's Lead Status Unknown lines of their construction era (plan 4.3; sheet Unknown-line shares).</t>
   </si>
   <si>
     <t>A zone is finished in the programme year in which the running total of the appropriation covers the running total of plan cost through it (plan 5.3). Lines rounded to the nearest ten and costs to the nearest $100,000; cumulative columns from unrounded zone costs.</t>
   </si>
   <si>
-    <t>Share of lines with no usable tap card expected to prove lead or GRR, by construction era</t>
-  </si>
-  <si>
-    <t>Lines with no usable tap card on the 78 main segments where every service line has been verified (each segment's lines exposed and verified together when its main was replaced, 2023 to 2026).</t>
+    <t>Share of the district's Lead Status Unknown lines expected to prove lead or GRR, by construction era</t>
+  </si>
+  <si>
+    <t>Lines built before 1989 with no usable tap card, all fourteen zones. Each is expected to prove lead or GRR at the share found on the 78 main segments where every service line has been verified (exposed together when the main was replaced, 2023 to 2026); the field verifications have already found part of that number, and the Lead Status Unknown lines carry the rest.</t>
   </si>
   <si>
     <t>Construction era</t>
   </si>
   <si>
+    <t>Lines with no usable tap card</t>
+  </si>
+  <si>
+    <t>Share on the segments verified whole</t>
+  </si>
+  <si>
+    <t>Expected to prove lead or GRR</t>
+  </si>
+  <si>
+    <t>Verified to date</t>
+  </si>
+  <si>
+    <t>Found lead or GRR</t>
+  </si>
+  <si>
+    <t>Lead Status Unknown</t>
+  </si>
+  <si>
+    <t>Expected lead or GRR among them</t>
+  </si>
+  <si>
+    <t>Share among Lead Status Unknown lines</t>
+  </si>
+  <si>
+    <t>Built before 1930</t>
+  </si>
+  <si>
+    <t>Built 1930 to 1949</t>
+  </si>
+  <si>
+    <t>Built 1950 to 1988</t>
+  </si>
+  <si>
+    <t>On the segments verified whole</t>
+  </si>
+  <si>
     <t>Lines verified</t>
   </si>
   <si>
-    <t>Found lead or GRR</t>
-  </si>
-  <si>
     <t>Share</t>
   </si>
   <si>
-    <t>Share across every verification (for comparison)</t>
-  </si>
-  <si>
-    <t>Built before 1930</t>
-  </si>
-  <si>
-    <t>Built 1930 to 1949</t>
-  </si>
-  <si>
-    <t>Built 1950 to 1988</t>
-  </si>
-  <si>
-    <t>Every other verification on file was a visit to one line because something pointed at it (a customer report, a sampling site, a leak on the service, the 2024 ranking), so its shares run high: priced at them the last zone would finish in 2039.</t>
+    <t>Every other verification on file was a visit to one line because something pointed at it (a customer report, a sampling site, a leak on the service, the 2024 ranking), so the lines still unknown are the ones those visits passed over. Priced at the whole-segment shares the last zone would finish in 2038; at the shares across every verification, in 2040.</t>
   </si>
   <si>
     <t>Paid per full replacement completed, 2026 replacement contracts</t>
@@ -712,13 +733,13 @@
         <v>11</v>
       </c>
       <c r="D5" s="4">
-        <v>1670</v>
+        <v>1560</v>
       </c>
       <c r="E5" s="5">
-        <v>23100000</v>
+        <v>21500000</v>
       </c>
       <c r="F5" s="6">
-        <v>23.1</v>
+        <v>21.5</v>
       </c>
       <c r="G5" s="7">
         <v>0.85</v>
@@ -738,16 +759,16 @@
         <v>13</v>
       </c>
       <c r="D6" s="4">
-        <v>2140</v>
+        <v>2020</v>
       </c>
       <c r="E6" s="5">
-        <v>34800000</v>
+        <v>33700000</v>
       </c>
       <c r="F6" s="6">
-        <v>57.9</v>
+        <v>55.2</v>
       </c>
       <c r="G6" s="7">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="H6" s="8">
         <v>2029</v>
@@ -764,16 +785,16 @@
         <v>15</v>
       </c>
       <c r="D7" s="4">
-        <v>1960</v>
+        <v>1830</v>
       </c>
       <c r="E7" s="5">
-        <v>29800000</v>
+        <v>28500000</v>
       </c>
       <c r="F7" s="6">
-        <v>87.7</v>
+        <v>83.7</v>
       </c>
       <c r="G7" s="7">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="H7" s="8">
         <v>2030</v>
@@ -790,16 +811,16 @@
         <v>17</v>
       </c>
       <c r="D8" s="4">
-        <v>1480</v>
+        <v>1420</v>
       </c>
       <c r="E8" s="5">
-        <v>24400000</v>
+        <v>23800000</v>
       </c>
       <c r="F8" s="6">
-        <v>112.1</v>
+        <v>107.5</v>
       </c>
       <c r="G8" s="7">
-        <v>4.14</v>
+        <v>4.23</v>
       </c>
       <c r="H8" s="8">
         <v>2031</v>
@@ -816,16 +837,16 @@
         <v>19</v>
       </c>
       <c r="D9" s="4">
-        <v>1830</v>
+        <v>1730</v>
       </c>
       <c r="E9" s="5">
-        <v>28100000</v>
+        <v>27100000</v>
       </c>
       <c r="F9" s="6">
-        <v>140.2</v>
+        <v>134.6</v>
       </c>
       <c r="G9" s="7">
-        <v>5.17</v>
+        <v>5.3</v>
       </c>
       <c r="H9" s="8">
         <v>2032</v>
@@ -842,16 +863,16 @@
         <v>21</v>
       </c>
       <c r="D10" s="4">
-        <v>1970</v>
+        <v>1840</v>
       </c>
       <c r="E10" s="5">
-        <v>28600000</v>
+        <v>27300000</v>
       </c>
       <c r="F10" s="6">
-        <v>168.9</v>
+        <v>161.9</v>
       </c>
       <c r="G10" s="7">
-        <v>6.23</v>
+        <v>6.37</v>
       </c>
       <c r="H10" s="8">
         <v>2033</v>
@@ -868,16 +889,16 @@
         <v>23</v>
       </c>
       <c r="D11" s="4">
-        <v>1750</v>
+        <v>1640</v>
       </c>
       <c r="E11" s="5">
-        <v>26800000</v>
+        <v>25700000</v>
       </c>
       <c r="F11" s="6">
-        <v>195.7</v>
+        <v>187.6</v>
       </c>
       <c r="G11" s="7">
-        <v>7.22</v>
+        <v>7.38</v>
       </c>
       <c r="H11" s="8">
         <v>2034</v>
@@ -894,19 +915,19 @@
         <v>25</v>
       </c>
       <c r="D12" s="4">
-        <v>930</v>
+        <v>1230</v>
       </c>
       <c r="E12" s="5">
-        <v>15200000</v>
+        <v>19600000</v>
       </c>
       <c r="F12" s="6">
-        <v>210.9</v>
+        <v>207.2</v>
       </c>
       <c r="G12" s="7">
-        <v>7.78</v>
+        <v>8.16</v>
       </c>
       <c r="H12" s="8">
-        <v>2034</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -920,16 +941,16 @@
         <v>27</v>
       </c>
       <c r="D13" s="4">
-        <v>1290</v>
+        <v>890</v>
       </c>
       <c r="E13" s="5">
-        <v>20300000</v>
+        <v>14800000</v>
       </c>
       <c r="F13" s="6">
-        <v>231.1</v>
+        <v>222</v>
       </c>
       <c r="G13" s="7">
-        <v>8.529999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="H13" s="8">
         <v>2035</v>
@@ -946,16 +967,16 @@
         <v>29</v>
       </c>
       <c r="D14" s="4">
-        <v>1380</v>
+        <v>1310</v>
       </c>
       <c r="E14" s="5">
-        <v>22100000</v>
+        <v>21400000</v>
       </c>
       <c r="F14" s="6">
-        <v>253.3</v>
+        <v>243.4</v>
       </c>
       <c r="G14" s="7">
-        <v>9.35</v>
+        <v>9.58</v>
       </c>
       <c r="H14" s="8">
         <v>2036</v>
@@ -972,19 +993,19 @@
         <v>31</v>
       </c>
       <c r="D15" s="4">
-        <v>770</v>
+        <v>1040</v>
       </c>
       <c r="E15" s="5">
-        <v>13000000</v>
+        <v>18000000</v>
       </c>
       <c r="F15" s="6">
-        <v>266.2</v>
+        <v>261.4</v>
       </c>
       <c r="G15" s="7">
-        <v>9.82</v>
+        <v>10.29</v>
       </c>
       <c r="H15" s="8">
-        <v>2036</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -998,16 +1019,16 @@
         <v>33</v>
       </c>
       <c r="D16" s="10">
-        <v>1080</v>
+        <v>750</v>
       </c>
       <c r="E16" s="11">
-        <v>18400000</v>
+        <v>12700000</v>
       </c>
       <c r="F16" s="12">
-        <v>284.7</v>
+        <v>274.1</v>
       </c>
       <c r="G16" s="13">
-        <v>10.5</v>
+        <v>10.79</v>
       </c>
       <c r="H16" s="14">
         <v>2037</v>
@@ -1022,10 +1043,10 @@
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
       <c r="F17" s="17">
-        <v>284.7</v>
+        <v>274.1</v>
       </c>
       <c r="G17" s="18">
-        <v>10.5</v>
+        <v>10.79</v>
       </c>
       <c r="H17" s="15"/>
     </row>
@@ -1051,27 +1072,31 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527D16E0-D497-5745-83E5-630E16E0894B}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>40</v>
       </c>
@@ -1087,61 +1112,170 @@
       <c r="E4" s="3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="4">
+        <v>12983</v>
+      </c>
+      <c r="C5" s="20">
+        <v>0.556</v>
+      </c>
+      <c r="D5" s="4">
+        <v>7213</v>
+      </c>
+      <c r="E5" s="4">
+        <v>2855</v>
+      </c>
+      <c r="F5" s="4">
+        <v>2177</v>
+      </c>
+      <c r="G5" s="4">
+        <v>10128</v>
+      </c>
+      <c r="H5" s="4">
+        <v>5036</v>
+      </c>
+      <c r="I5" s="20">
+        <v>0.497</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="4">
+        <v>10612</v>
+      </c>
+      <c r="C6" s="20">
+        <v>0.316</v>
+      </c>
+      <c r="D6" s="4">
+        <v>3351</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1281</v>
+      </c>
+      <c r="F6" s="4">
+        <v>749</v>
+      </c>
+      <c r="G6" s="4">
+        <v>9331</v>
+      </c>
+      <c r="H6" s="4">
+        <v>2602</v>
+      </c>
+      <c r="I6" s="20">
+        <v>0.279</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="4">
+        <v>13279</v>
+      </c>
+      <c r="C7" s="20">
+        <v>0.083</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1107</v>
+      </c>
+      <c r="E7" s="4">
+        <v>775</v>
+      </c>
+      <c r="F7" s="4">
+        <v>168</v>
+      </c>
+      <c r="G7" s="4">
+        <v>12504</v>
+      </c>
+      <c r="H7" s="4">
+        <v>939</v>
+      </c>
+      <c r="I7" s="20">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B5">
+      <c r="D10" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11">
         <v>792</v>
       </c>
-      <c r="C5">
+      <c r="C11">
         <v>440</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D11" s="20">
         <v>0.556</v>
       </c>
-      <c r="E5" s="20">
-        <v>0.763</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6">
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12">
         <v>304</v>
       </c>
-      <c r="C6">
+      <c r="C12">
         <v>96</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D12" s="20">
         <v>0.316</v>
       </c>
-      <c r="E6" s="20">
-        <v>0.585</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7">
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13">
         <v>168</v>
       </c>
-      <c r="C7">
+      <c r="C13">
         <v>14</v>
       </c>
-      <c r="D7" s="20">
+      <c r="D13" s="20">
         <v>0.083</v>
       </c>
-      <c r="E7" s="20">
-        <v>0.217</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
-        <v>48</v>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1164,40 +1298,40 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C5" s="4">
         <v>13890</v>
@@ -1214,10 +1348,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B6" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C6" s="4">
         <v>14509</v>
@@ -1234,10 +1368,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C7" s="4">
         <v>14488</v>
@@ -1254,15 +1388,15 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C10">
         <v>71</v>
@@ -1279,10 +1413,10 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C11">
         <v>41</v>
@@ -1299,10 +1433,10 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="C12">
         <v>23</v>
@@ -1319,7 +1453,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1340,12 +1474,12 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.25">
@@ -1359,7 +1493,7 @@
         <v>4</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1471,7 +1605,7 @@
         <v>25</v>
       </c>
       <c r="D12" s="4">
-        <v>518</v>
+        <v>626</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1485,7 +1619,7 @@
         <v>27</v>
       </c>
       <c r="D13" s="4">
-        <v>626</v>
+        <v>518</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1513,7 +1647,7 @@
         <v>31</v>
       </c>
       <c r="D15" s="4">
-        <v>368</v>
+        <v>539</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1527,7 +1661,7 @@
         <v>33</v>
       </c>
       <c r="D16" s="4">
-        <v>539</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>

--- a/task124/golden/lslr_2027_programme.xlsx
+++ b/task124/golden/lslr_2027_programme.xlsx
@@ -12,6 +12,14 @@
     <sheet name="2026 contract payments" sheetId="3" r:id="rId3"/>
     <sheet name="Access agreements" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Zone schedule'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Zone schedule'!$A$1:$H$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Unknown-line shares'!$A$1:$G$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'2026 contract payments'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Access agreements'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Access agreements'!$A$1:$D$16</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -22,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="81">
   <si>
     <t>Every zone finished by 2037 at $25.4 million a year: lead service line replacement schedule, 2027 to 2037</t>
   </si>
@@ -96,40 +104,40 @@
     <t>Depot Square</t>
   </si>
   <si>
+    <t>RZ-12</t>
+  </si>
+  <si>
+    <t>Kittering Village</t>
+  </si>
+  <si>
     <t>RZ-03</t>
   </si>
   <si>
     <t>Millrace</t>
   </si>
   <si>
-    <t>RZ-12</t>
-  </si>
-  <si>
-    <t>Kittering Village</t>
-  </si>
-  <si>
     <t>RZ-08</t>
   </si>
   <si>
     <t>Elm Park</t>
   </si>
   <si>
+    <t>RZ-10</t>
+  </si>
+  <si>
+    <t>Lakeview Terrace</t>
+  </si>
+  <si>
     <t>RZ-06</t>
   </si>
   <si>
     <t>Wexley</t>
   </si>
   <si>
-    <t>RZ-10</t>
-  </si>
-  <si>
-    <t>Lakeview Terrace</t>
-  </si>
-  <si>
     <t>All twelve zones</t>
   </si>
   <si>
-    <t>Last zone: RZ-10 Lakeview Terrace, finished in programme year 2037, inside the 1 November 2037 deadline.</t>
+    <t>Last zone: RZ-06 Wexley, finished in programme year 2037, inside the 1 November 2037 deadline.</t>
   </si>
   <si>
     <t>Lines to replace: the zone's Lead and GRR lines plus its Lead Status Unknown lines at the share of lead or GRR expected among the district's Lead Status Unknown lines of their construction era (plan 4.3; sheet Unknown-line shares).</t>
@@ -141,33 +149,24 @@
     <t>Share of the district's Lead Status Unknown lines expected to prove lead or GRR, by construction era</t>
   </si>
   <si>
-    <t>Lines built before 1989 with no usable tap card, all fourteen zones. Each is expected to prove lead or GRR at the share found on the 78 main segments where every service line has been verified (exposed together when the main was replaced, 2023 to 2026); the field verifications have already found part of that number, and the Lead Status Unknown lines carry the rest.</t>
+    <t>All fourteen zones. Each unknown line is costed at the rate found on the verified lines with no tap card on mains of the same kind: mains whose tap cards read lead or galvanized, and mains whose cards read only copper or plastic.</t>
   </si>
   <si>
     <t>Construction era</t>
   </si>
   <si>
-    <t>Lines with no usable tap card</t>
-  </si>
-  <si>
-    <t>Share on the segments verified whole</t>
+    <t>Unknown lines on lead or galvanized mains</t>
+  </si>
+  <si>
+    <t>Unknown lines on copper or plastic mains</t>
+  </si>
+  <si>
+    <t>Lead Status Unknown lines</t>
   </si>
   <si>
     <t>Expected to prove lead or GRR</t>
   </si>
   <si>
-    <t>Verified to date</t>
-  </si>
-  <si>
-    <t>Found lead or GRR</t>
-  </si>
-  <si>
-    <t>Lead Status Unknown</t>
-  </si>
-  <si>
-    <t>Expected lead or GRR among them</t>
-  </si>
-  <si>
     <t>Share among Lead Status Unknown lines</t>
   </si>
   <si>
@@ -180,16 +179,43 @@
     <t>Built 1950 to 1988</t>
   </si>
   <si>
-    <t>On the segments verified whole</t>
-  </si>
-  <si>
-    <t>Lines verified</t>
+    <t>Verified lines with no tap card, first result</t>
+  </si>
+  <si>
+    <t>Main's tap cards</t>
+  </si>
+  <si>
+    <t>On the replaced mains: verified</t>
+  </si>
+  <si>
+    <t>found lead or GRR</t>
+  </si>
+  <si>
+    <t>Other verifications: verified</t>
   </si>
   <si>
     <t>Share</t>
   </si>
   <si>
-    <t>Every other verification on file was a visit to one line because something pointed at it (a customer report, a sampling site, a leak on the service, the 2024 ranking), so the lines still unknown are the ones those visits passed over. Priced at the whole-segment shares the last zone would finish in 2038; at the shares across every verification, in 2040.</t>
+    <t>Lead or galvanized</t>
+  </si>
+  <si>
+    <t>Copper or plastic only</t>
+  </si>
+  <si>
+    <t>Lines on lead or galvanized mains, per cent of each group</t>
+  </si>
+  <si>
+    <t>Verified lines with no tap card</t>
+  </si>
+  <si>
+    <t>Lines on the replaced mains</t>
+  </si>
+  <si>
+    <t>Tap card lines</t>
+  </si>
+  <si>
+    <t>The lines verified so far and the surviving tap cards sit on lead or galvanized mains far more often than the lines still unknown, and so do the replaced mains built before 1950 (those built later are all on copper or plastic mains), so a rate taken from any of them across a whole era misstates the unknown lines: at the shares across every verification the plan would run to 2042, at the shares on the replaced mains to 2040, and at the tap card lines' share to 2039.</t>
   </si>
   <si>
     <t>Paid per full replacement completed, 2026 replacement contracts</t>
@@ -243,7 +269,7 @@
     <t>Service lines with a signed access agreement, by zone, 8 January 2027</t>
   </si>
   <si>
-    <t>Distinct service lines with a right-of-entry agreement signed and not withdrawn, counted in the zone the inventory gives the line today.</t>
+    <t>Distinct service lines open in the plan with a right-of-entry agreement signed and not withdrawn: forms in the agreement system, and forms the owner e-signed on the portal that the agreement system does not hold; counted in the zone the inventory gives the line today.</t>
   </si>
   <si>
     <t>Service lines with a signed agreement</t>
@@ -673,6 +699,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49D1E1FC-E7C2-52D1-8378-86FA5D5A1F4F}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -733,16 +762,16 @@
         <v>11</v>
       </c>
       <c r="D5" s="4">
-        <v>1560</v>
+        <v>1250</v>
       </c>
       <c r="E5" s="5">
-        <v>21500000</v>
+        <v>20700000</v>
       </c>
       <c r="F5" s="6">
-        <v>21.5</v>
+        <v>20.7</v>
       </c>
       <c r="G5" s="7">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H5" s="8">
         <v>2027</v>
@@ -759,16 +788,16 @@
         <v>13</v>
       </c>
       <c r="D6" s="4">
-        <v>2020</v>
+        <v>1820</v>
       </c>
       <c r="E6" s="5">
-        <v>33700000</v>
+        <v>34000000</v>
       </c>
       <c r="F6" s="6">
-        <v>55.2</v>
+        <v>54.7</v>
       </c>
       <c r="G6" s="7">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="H6" s="8">
         <v>2029</v>
@@ -785,16 +814,16 @@
         <v>15</v>
       </c>
       <c r="D7" s="4">
-        <v>1830</v>
+        <v>1650</v>
       </c>
       <c r="E7" s="5">
-        <v>28500000</v>
+        <v>28400000</v>
       </c>
       <c r="F7" s="6">
-        <v>83.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="G7" s="7">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="H7" s="8">
         <v>2030</v>
@@ -811,16 +840,16 @@
         <v>17</v>
       </c>
       <c r="D8" s="4">
-        <v>1420</v>
+        <v>1180</v>
       </c>
       <c r="E8" s="5">
-        <v>23800000</v>
+        <v>23000000</v>
       </c>
       <c r="F8" s="6">
-        <v>107.5</v>
+        <v>106.1</v>
       </c>
       <c r="G8" s="7">
-        <v>4.23</v>
+        <v>4.18</v>
       </c>
       <c r="H8" s="8">
         <v>2031</v>
@@ -837,16 +866,16 @@
         <v>19</v>
       </c>
       <c r="D9" s="4">
-        <v>1730</v>
+        <v>1380</v>
       </c>
       <c r="E9" s="5">
-        <v>27100000</v>
+        <v>25000000</v>
       </c>
       <c r="F9" s="6">
-        <v>134.6</v>
+        <v>131.1</v>
       </c>
       <c r="G9" s="7">
-        <v>5.3</v>
+        <v>5.16</v>
       </c>
       <c r="H9" s="8">
         <v>2032</v>
@@ -863,16 +892,16 @@
         <v>21</v>
       </c>
       <c r="D10" s="4">
-        <v>1840</v>
+        <v>1540</v>
       </c>
       <c r="E10" s="5">
-        <v>27300000</v>
+        <v>26000000</v>
       </c>
       <c r="F10" s="6">
-        <v>161.9</v>
+        <v>157.1</v>
       </c>
       <c r="G10" s="7">
-        <v>6.37</v>
+        <v>6.18</v>
       </c>
       <c r="H10" s="8">
         <v>2033</v>
@@ -889,16 +918,16 @@
         <v>23</v>
       </c>
       <c r="D11" s="4">
-        <v>1640</v>
+        <v>1390</v>
       </c>
       <c r="E11" s="5">
-        <v>25700000</v>
+        <v>24500000</v>
       </c>
       <c r="F11" s="6">
-        <v>187.6</v>
+        <v>181.6</v>
       </c>
       <c r="G11" s="7">
-        <v>7.38</v>
+        <v>7.15</v>
       </c>
       <c r="H11" s="8">
         <v>2034</v>
@@ -915,19 +944,19 @@
         <v>25</v>
       </c>
       <c r="D12" s="4">
-        <v>1230</v>
+        <v>760</v>
       </c>
       <c r="E12" s="5">
-        <v>19600000</v>
+        <v>14700000</v>
       </c>
       <c r="F12" s="6">
-        <v>207.2</v>
+        <v>196.3</v>
       </c>
       <c r="G12" s="7">
-        <v>8.16</v>
+        <v>7.73</v>
       </c>
       <c r="H12" s="8">
-        <v>2035</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -941,16 +970,16 @@
         <v>27</v>
       </c>
       <c r="D13" s="4">
-        <v>890</v>
+        <v>1050</v>
       </c>
       <c r="E13" s="5">
-        <v>14800000</v>
+        <v>19100000</v>
       </c>
       <c r="F13" s="6">
-        <v>222</v>
+        <v>215.4</v>
       </c>
       <c r="G13" s="7">
-        <v>8.74</v>
+        <v>8.48</v>
       </c>
       <c r="H13" s="8">
         <v>2035</v>
@@ -967,16 +996,16 @@
         <v>29</v>
       </c>
       <c r="D14" s="4">
-        <v>1310</v>
+        <v>1170</v>
       </c>
       <c r="E14" s="5">
-        <v>21400000</v>
+        <v>21500000</v>
       </c>
       <c r="F14" s="6">
-        <v>243.4</v>
+        <v>236.9</v>
       </c>
       <c r="G14" s="7">
-        <v>9.58</v>
+        <v>9.33</v>
       </c>
       <c r="H14" s="8">
         <v>2036</v>
@@ -993,19 +1022,19 @@
         <v>31</v>
       </c>
       <c r="D15" s="4">
-        <v>1040</v>
+        <v>670</v>
       </c>
       <c r="E15" s="5">
-        <v>18000000</v>
+        <v>13300000</v>
       </c>
       <c r="F15" s="6">
-        <v>261.4</v>
+        <v>250.2</v>
       </c>
       <c r="G15" s="7">
-        <v>10.29</v>
+        <v>9.85</v>
       </c>
       <c r="H15" s="8">
-        <v>2037</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1019,16 +1048,16 @@
         <v>33</v>
       </c>
       <c r="D16" s="10">
-        <v>750</v>
+        <v>890</v>
       </c>
       <c r="E16" s="11">
-        <v>12700000</v>
+        <v>18100000</v>
       </c>
       <c r="F16" s="12">
-        <v>274.1</v>
+        <v>268.3</v>
       </c>
       <c r="G16" s="13">
-        <v>10.79</v>
+        <v>10.56</v>
       </c>
       <c r="H16" s="14">
         <v>2037</v>
@@ -1043,10 +1072,10 @@
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
       <c r="F17" s="17">
-        <v>274.1</v>
+        <v>268.3</v>
       </c>
       <c r="G17" s="18">
-        <v>10.79</v>
+        <v>10.56</v>
       </c>
       <c r="H17" s="15"/>
     </row>
@@ -1067,36 +1096,38 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527D16E0-D497-5745-83E5-630E16E0894B}">
-  <dimension ref="A1:I15"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>40</v>
       </c>
@@ -1115,176 +1146,322 @@
       <c r="F4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="B5" s="4">
+        <v>3822</v>
+      </c>
+      <c r="C5" s="4">
+        <v>6117</v>
+      </c>
+      <c r="D5" s="4">
+        <v>9939</v>
+      </c>
+      <c r="E5" s="4">
+        <v>3871</v>
+      </c>
+      <c r="F5" s="20">
+        <v>0.389</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>47</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="B6" s="4">
+        <v>2215</v>
+      </c>
+      <c r="C6" s="4">
+        <v>6808</v>
+      </c>
+      <c r="D6" s="4">
+        <v>9023</v>
+      </c>
+      <c r="E6" s="4">
+        <v>2415</v>
+      </c>
+      <c r="F6" s="20">
+        <v>0.268</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B7" s="4">
+        <v>359</v>
+      </c>
+      <c r="C7" s="4">
+        <v>14210</v>
+      </c>
+      <c r="D7" s="4">
+        <v>14569</v>
+      </c>
+      <c r="E7" s="4">
+        <v>1081</v>
+      </c>
+      <c r="F7" s="20">
+        <v>0.074</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="4">
-        <v>12983</v>
-      </c>
-      <c r="C5" s="20">
-        <v>0.556</v>
-      </c>
-      <c r="D5" s="4">
-        <v>7213</v>
-      </c>
-      <c r="E5" s="4">
-        <v>2855</v>
-      </c>
-      <c r="F5" s="4">
-        <v>2177</v>
-      </c>
-      <c r="G5" s="4">
-        <v>10128</v>
-      </c>
-      <c r="H5" s="4">
-        <v>5036</v>
-      </c>
-      <c r="I5" s="20">
-        <v>0.497</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    </row>
+    <row r="10" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="4">
-        <v>10612</v>
-      </c>
-      <c r="C6" s="20">
-        <v>0.316</v>
-      </c>
-      <c r="D6" s="4">
-        <v>3351</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1281</v>
-      </c>
-      <c r="F6" s="4">
-        <v>749</v>
-      </c>
-      <c r="G6" s="4">
-        <v>9331</v>
-      </c>
-      <c r="H6" s="4">
-        <v>2602</v>
-      </c>
-      <c r="I6" s="20">
-        <v>0.279</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="4">
-        <v>13279</v>
-      </c>
-      <c r="C7" s="20">
-        <v>0.083</v>
-      </c>
-      <c r="D7" s="4">
-        <v>1107</v>
-      </c>
-      <c r="E7" s="4">
-        <v>775</v>
-      </c>
-      <c r="F7" s="4">
+      <c r="D10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="4">
+        <v>798</v>
+      </c>
+      <c r="D11" s="4">
+        <v>741</v>
+      </c>
+      <c r="E11" s="4">
+        <v>1176</v>
+      </c>
+      <c r="F11" s="4">
+        <v>1092</v>
+      </c>
+      <c r="G11" s="20">
+        <v>0.929</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="4">
         <v>168</v>
       </c>
-      <c r="G7" s="4">
-        <v>12504</v>
-      </c>
-      <c r="H7" s="4">
-        <v>939</v>
-      </c>
-      <c r="I7" s="20">
-        <v>0.075</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="D12" s="4">
+        <v>156</v>
+      </c>
+      <c r="E12" s="4">
+        <v>546</v>
+      </c>
+      <c r="F12" s="4">
+        <v>507</v>
+      </c>
+      <c r="G12" s="20">
+        <v>0.929</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="4">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4">
+        <v>56</v>
+      </c>
+      <c r="F13" s="4">
         <v>52</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+      <c r="G13" s="20">
+        <v>0.929</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="4">
+        <v>19</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
+        <v>171</v>
+      </c>
+      <c r="F14" s="4">
+        <v>9</v>
+      </c>
+      <c r="G14" s="20">
+        <v>0.053</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="4">
+        <v>114</v>
+      </c>
+      <c r="D15" s="4">
+        <v>6</v>
+      </c>
+      <c r="E15" s="4">
+        <v>133</v>
+      </c>
+      <c r="F15" s="4">
+        <v>7</v>
+      </c>
+      <c r="G15" s="20">
+        <v>0.053</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="4">
+        <v>19</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>209</v>
+      </c>
+      <c r="F16" s="4">
+        <v>11</v>
+      </c>
+      <c r="G16" s="20">
+        <v>0.053</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="8">
+        <v>38</v>
+      </c>
+      <c r="C20" s="8">
+        <v>91</v>
+      </c>
+      <c r="D20" s="8">
+        <v>98</v>
+      </c>
+      <c r="E20" s="8">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="8">
+        <v>25</v>
+      </c>
+      <c r="C21" s="8">
+        <v>74</v>
+      </c>
+      <c r="D21" s="8">
+        <v>60</v>
+      </c>
+      <c r="E21" s="8">
         <v>53</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11">
-        <v>792</v>
-      </c>
-      <c r="C11">
-        <v>440</v>
-      </c>
-      <c r="D11" s="20">
-        <v>0.556</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12">
-        <v>304</v>
-      </c>
-      <c r="C12">
-        <v>96</v>
-      </c>
-      <c r="D12" s="20">
-        <v>0.316</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13">
-        <v>168</v>
-      </c>
-      <c r="C13">
-        <v>14</v>
-      </c>
-      <c r="D13" s="20">
-        <v>0.083</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
-        <v>55</v>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="8">
+        <v>2</v>
+      </c>
+      <c r="C22" s="8">
+        <v>20</v>
+      </c>
+      <c r="D22" s="8">
+        <v>0</v>
+      </c>
+      <c r="E22" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="19" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C393FDBE-6763-5433-801F-77744CED4AD0}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1298,171 +1475,175 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C5" s="4">
-        <v>13890</v>
+        <v>14395</v>
       </c>
       <c r="D5" s="4">
-        <v>13494</v>
+        <v>13488</v>
       </c>
       <c r="E5" s="4">
-        <v>13416</v>
+        <v>13407</v>
       </c>
       <c r="F5" s="4">
-        <v>13673</v>
+        <v>13344</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C6" s="4">
-        <v>14509</v>
+        <v>14634</v>
       </c>
       <c r="D6" s="4">
-        <v>13937</v>
+        <v>13985</v>
       </c>
       <c r="E6" s="4">
-        <v>13903</v>
+        <v>13922</v>
       </c>
       <c r="F6" s="4">
-        <v>13568</v>
+        <v>13867</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C7" s="4">
-        <v>14488</v>
+        <v>15294</v>
       </c>
       <c r="D7" s="4">
-        <v>14459</v>
+        <v>14515</v>
       </c>
       <c r="E7" s="4">
-        <v>15008</v>
+        <v>14636</v>
       </c>
       <c r="F7" s="4">
-        <v>14784</v>
+        <v>14444</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="21" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10">
         <v>71</v>
       </c>
-      <c r="D10">
-        <v>90</v>
-      </c>
-      <c r="E10">
-        <v>162</v>
-      </c>
-      <c r="F10">
-        <v>61</v>
+      <c r="C10" s="4">
+        <v>33</v>
+      </c>
+      <c r="D10" s="4">
+        <v>87</v>
+      </c>
+      <c r="E10" s="4">
+        <v>194</v>
+      </c>
+      <c r="F10" s="4">
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11">
-        <v>41</v>
-      </c>
-      <c r="D11">
-        <v>85</v>
-      </c>
-      <c r="E11">
-        <v>132</v>
-      </c>
-      <c r="F11">
-        <v>53</v>
+        <v>73</v>
+      </c>
+      <c r="C11" s="4">
+        <v>30</v>
+      </c>
+      <c r="D11" s="4">
+        <v>83</v>
+      </c>
+      <c r="E11" s="4">
+        <v>137</v>
+      </c>
+      <c r="F11" s="4">
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C12">
-        <v>23</v>
-      </c>
-      <c r="D12">
-        <v>20</v>
-      </c>
-      <c r="E12">
-        <v>21</v>
-      </c>
-      <c r="F12">
-        <v>13</v>
+        <v>75</v>
+      </c>
+      <c r="C12" s="4">
+        <v>34</v>
+      </c>
+      <c r="D12" s="4">
+        <v>56</v>
+      </c>
+      <c r="E12" s="4">
+        <v>103</v>
+      </c>
+      <c r="F12" s="4">
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DF335C8-0E0F-58F5-9598-969071AB7135}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1474,12 +1655,12 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.25">
@@ -1493,7 +1674,7 @@
         <v>4</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1507,7 +1688,7 @@
         <v>11</v>
       </c>
       <c r="D5" s="4">
-        <v>975</v>
+        <v>960</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1521,7 +1702,7 @@
         <v>13</v>
       </c>
       <c r="D6" s="4">
-        <v>1217</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1535,7 +1716,7 @@
         <v>15</v>
       </c>
       <c r="D7" s="4">
-        <v>1118</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1549,7 +1730,7 @@
         <v>17</v>
       </c>
       <c r="D8" s="4">
-        <v>954</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1563,7 +1744,7 @@
         <v>19</v>
       </c>
       <c r="D9" s="4">
-        <v>1017</v>
+        <v>991</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1577,7 +1758,7 @@
         <v>21</v>
       </c>
       <c r="D10" s="4">
-        <v>857</v>
+        <v>878</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1591,7 +1772,7 @@
         <v>23</v>
       </c>
       <c r="D11" s="4">
-        <v>889</v>
+        <v>846</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1605,7 +1786,7 @@
         <v>25</v>
       </c>
       <c r="D12" s="4">
-        <v>626</v>
+        <v>504</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1619,7 +1800,7 @@
         <v>27</v>
       </c>
       <c r="D13" s="4">
-        <v>518</v>
+        <v>633</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1633,7 +1814,7 @@
         <v>29</v>
       </c>
       <c r="D14" s="4">
-        <v>663</v>
+        <v>685</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1647,7 +1828,7 @@
         <v>31</v>
       </c>
       <c r="D15" s="4">
-        <v>539</v>
+        <v>386</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1661,10 +1842,11 @@
         <v>33</v>
       </c>
       <c r="D16" s="4">
-        <v>368</v>
+        <v>607</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/task124/golden/lslr_2027_programme.xlsx
+++ b/task124/golden/lslr_2027_programme.xlsx
@@ -14,8 +14,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Zone schedule'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Zone schedule'!$A$1:$H$21</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Unknown-line shares'!$A$1:$G$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Zone schedule'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Unknown-line shares'!$A$1:$G$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'2026 contract payments'!$A$1:$F$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Access agreements'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Access agreements'!$A$1:$D$16</definedName>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="82">
   <si>
     <t>Every zone finished by 2037 at $25.4 million a year: lead service line replacement schedule, 2027 to 2037</t>
   </si>
@@ -53,10 +53,7 @@
     <t>Plan cost ($)</t>
   </si>
   <si>
-    <t>Cumulative plan cost ($ million)</t>
-  </si>
-  <si>
-    <t>Cumulative programme years</t>
+    <t>Work starts (programme year)</t>
   </si>
   <si>
     <t>Finish year</t>
@@ -137,19 +134,25 @@
     <t>All twelve zones</t>
   </si>
   <si>
-    <t>Last zone: RZ-06 Wexley, finished in programme year 2037, inside the 1 November 2037 deadline.</t>
+    <t>$267 million</t>
+  </si>
+  <si>
+    <t>10.5 years</t>
+  </si>
+  <si>
+    <t>Last zone: RZ-06 Wexley, finished in programme year 2037, inside the 1 November 2037 deadline. The twelve zones cost $267 million, 10.5 years of the $25.4 million appropriation.</t>
   </si>
   <si>
     <t>Lines to replace: the zone's Lead and GRR lines plus its Lead Status Unknown lines at the share of lead or GRR expected among the district's Lead Status Unknown lines of their construction era (plan 4.3; sheet Unknown-line shares).</t>
   </si>
   <si>
-    <t>A zone is finished in the programme year in which the running total of the appropriation covers the running total of plan cost through it (plan 5.3). Lines rounded to the nearest ten and costs to the nearest $100,000; cumulative columns from unrounded zone costs.</t>
+    <t>A zone is finished in the programme year in which the running total of the appropriation covers the running total of plan cost through it (plan 5.3); its work starts when the zone before it is finished (plan 5.2). Lines rounded to the nearest ten and costs to the nearest $100,000, from unrounded expected lines.</t>
   </si>
   <si>
     <t>Share of the district's Lead Status Unknown lines expected to prove lead or GRR, by construction era</t>
   </si>
   <si>
-    <t>All fourteen zones. Each unknown line is costed at the rate found on the verified lines with no tap card on mains of the same kind: mains whose tap cards read lead or galvanized, and mains whose cards read only copper or plastic.</t>
+    <t>All fourteen zones. Each unknown line is costed at the rate found on the verified lines with no tap card on mains of the same kind built in the same era: mains whose tap cards read lead or galvanized, and mains whose cards read only copper or plastic.</t>
   </si>
   <si>
     <t>Construction era</t>
@@ -164,9 +167,6 @@
     <t>Lead Status Unknown lines</t>
   </si>
   <si>
-    <t>Expected to prove lead or GRR</t>
-  </si>
-  <si>
     <t>Share among Lead Status Unknown lines</t>
   </si>
   <si>
@@ -194,7 +194,7 @@
     <t>Other verifications: verified</t>
   </si>
   <si>
-    <t>Share</t>
+    <t>Found lead or GRR (%)</t>
   </si>
   <si>
     <t>Lead or galvanized</t>
@@ -215,7 +215,10 @@
     <t>Tap card lines</t>
   </si>
   <si>
-    <t>The lines verified so far and the surviving tap cards sit on lead or galvanized mains far more often than the lines still unknown, and so do the replaced mains built before 1950 (those built later are all on copper or plastic mains), so a rate taken from any of them across a whole era misstates the unknown lines: at the shares across every verification the plan would run to 2042, at the shares on the replaced mains to 2040, and at the tap card lines' share to 2039.</t>
+    <t>On lead or galvanized mains the share found falls with the era the line was built, so each era is costed at its own rate; one rate for each kind of main across all eras (0.963 on lead or galvanized mains) would change the rounded lines in 9 of the twelve zones.</t>
+  </si>
+  <si>
+    <t>The lines verified so far and the surviving tap cards sit on lead or galvanized mains far more often than the lines still unknown, so a rate taken from any of them across a whole era misstates the unknown lines: at the shares across every verification the plan would run to 2039, at the shares on the replaced mains to 2041, and at the tap card lines' share to 2040.</t>
   </si>
   <si>
     <t>Paid per full replacement completed, 2026 replacement contracts</t>
@@ -279,10 +282,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -372,7 +374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -381,22 +383,20 @@
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -702,7 +702,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" customWidth="1"/>
@@ -710,22 +710,21 @@
     <col min="3" max="3" width="18.7109375" customWidth="1"/>
     <col min="4" max="4" width="14.7109375" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -747,351 +746,311 @@
       <c r="G4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
       <c r="D5" s="4">
-        <v>1250</v>
+        <v>1210</v>
       </c>
       <c r="E5" s="5">
-        <v>20700000</v>
+        <v>20800000</v>
       </c>
       <c r="F5" s="6">
-        <v>20.7</v>
-      </c>
-      <c r="G5" s="7">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="H5" s="8">
         <v>2027</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G5" s="6">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
       <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
       <c r="D6" s="4">
-        <v>1820</v>
+        <v>1710</v>
       </c>
       <c r="E6" s="5">
-        <v>34000000</v>
+        <v>34300000</v>
       </c>
       <c r="F6" s="6">
-        <v>54.7</v>
-      </c>
-      <c r="G6" s="7">
-        <v>2.15</v>
-      </c>
-      <c r="H6" s="8">
+        <v>2027</v>
+      </c>
+      <c r="G6" s="6">
         <v>2029</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
       <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
         <v>14</v>
       </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
       <c r="D7" s="4">
-        <v>1650</v>
+        <v>1570</v>
       </c>
       <c r="E7" s="5">
-        <v>28400000</v>
+        <v>28900000</v>
       </c>
       <c r="F7" s="6">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="G7" s="7">
-        <v>3.27</v>
-      </c>
-      <c r="H7" s="8">
+        <v>2029</v>
+      </c>
+      <c r="G7" s="6">
         <v>2030</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
       <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
       <c r="D8" s="4">
-        <v>1180</v>
+        <v>1070</v>
       </c>
       <c r="E8" s="5">
-        <v>23000000</v>
+        <v>22900000</v>
       </c>
       <c r="F8" s="6">
-        <v>106.1</v>
-      </c>
-      <c r="G8" s="7">
-        <v>4.18</v>
-      </c>
-      <c r="H8" s="8">
+        <v>2030</v>
+      </c>
+      <c r="G8" s="6">
         <v>2031</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
       <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
         <v>18</v>
       </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
       <c r="D9" s="4">
-        <v>1380</v>
+        <v>1440</v>
       </c>
       <c r="E9" s="5">
-        <v>25000000</v>
+        <v>26100000</v>
       </c>
       <c r="F9" s="6">
-        <v>131.1</v>
-      </c>
-      <c r="G9" s="7">
-        <v>5.16</v>
-      </c>
-      <c r="H9" s="8">
+        <v>2031</v>
+      </c>
+      <c r="G9" s="6">
         <v>2032</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
       <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
         <v>20</v>
       </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
       <c r="D10" s="4">
-        <v>1540</v>
+        <v>1730</v>
       </c>
       <c r="E10" s="5">
-        <v>26000000</v>
+        <v>29900000</v>
       </c>
       <c r="F10" s="6">
-        <v>157.1</v>
-      </c>
-      <c r="G10" s="7">
-        <v>6.18</v>
-      </c>
-      <c r="H10" s="8">
+        <v>2032</v>
+      </c>
+      <c r="G10" s="6">
         <v>2033</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7</v>
       </c>
       <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
         <v>22</v>
       </c>
-      <c r="C11" t="s">
-        <v>23</v>
-      </c>
       <c r="D11" s="4">
-        <v>1390</v>
+        <v>1320</v>
       </c>
       <c r="E11" s="5">
-        <v>24500000</v>
+        <v>24900000</v>
       </c>
       <c r="F11" s="6">
-        <v>181.6</v>
-      </c>
-      <c r="G11" s="7">
-        <v>7.15</v>
-      </c>
-      <c r="H11" s="8">
+        <v>2033</v>
+      </c>
+      <c r="G11" s="6">
         <v>2034</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
       <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
         <v>24</v>
       </c>
-      <c r="C12" t="s">
-        <v>25</v>
-      </c>
       <c r="D12" s="4">
-        <v>760</v>
+        <v>550</v>
       </c>
       <c r="E12" s="5">
-        <v>14700000</v>
+        <v>11900000</v>
       </c>
       <c r="F12" s="6">
-        <v>196.3</v>
-      </c>
-      <c r="G12" s="7">
-        <v>7.73</v>
-      </c>
-      <c r="H12" s="8">
         <v>2034</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G12" s="6">
+        <v>2034</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
       <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
         <v>26</v>
       </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
       <c r="D13" s="4">
-        <v>1050</v>
+        <v>1020</v>
       </c>
       <c r="E13" s="5">
-        <v>19100000</v>
+        <v>19500000</v>
       </c>
       <c r="F13" s="6">
-        <v>215.4</v>
-      </c>
-      <c r="G13" s="7">
-        <v>8.48</v>
-      </c>
-      <c r="H13" s="8">
+        <v>2034</v>
+      </c>
+      <c r="G13" s="6">
         <v>2035</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>10</v>
       </c>
       <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
         <v>28</v>
       </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
       <c r="D14" s="4">
-        <v>1170</v>
+        <v>1080</v>
       </c>
       <c r="E14" s="5">
-        <v>21500000</v>
+        <v>21200000</v>
       </c>
       <c r="F14" s="6">
-        <v>236.9</v>
-      </c>
-      <c r="G14" s="7">
-        <v>9.33</v>
-      </c>
-      <c r="H14" s="8">
+        <v>2035</v>
+      </c>
+      <c r="G14" s="6">
         <v>2036</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>11</v>
       </c>
       <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
         <v>30</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" s="4">
+        <v>450</v>
+      </c>
+      <c r="E15" s="5">
+        <v>10100000</v>
+      </c>
+      <c r="F15" s="6">
+        <v>2036</v>
+      </c>
+      <c r="G15" s="6">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="7">
+        <v>12</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="4">
-        <v>670</v>
-      </c>
-      <c r="E15" s="5">
-        <v>13300000</v>
-      </c>
-      <c r="F15" s="6">
-        <v>250.2</v>
-      </c>
-      <c r="G15" s="7">
-        <v>9.85</v>
-      </c>
-      <c r="H15" s="8">
+      <c r="C16" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="8">
+        <v>710</v>
+      </c>
+      <c r="E16" s="9">
+        <v>16600000</v>
+      </c>
+      <c r="F16" s="10">
         <v>2036</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="9">
-        <v>12</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="9" t="s">
+      <c r="G16" s="10">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="10">
-        <v>890</v>
-      </c>
-      <c r="E16" s="11">
-        <v>18100000</v>
-      </c>
-      <c r="F16" s="12">
-        <v>268.3</v>
-      </c>
-      <c r="G16" s="13">
-        <v>10.56</v>
-      </c>
-      <c r="H16" s="14">
-        <v>2037</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="16" t="s">
+      <c r="D17" s="11"/>
+      <c r="E17" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="17">
-        <v>268.3</v>
-      </c>
-      <c r="G17" s="18">
-        <v>10.56</v>
-      </c>
-      <c r="H17" s="15"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+      <c r="F17" s="13" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="G17" s="11"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
         <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1105,7 +1064,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1114,36 +1073,33 @@
     <col min="4" max="4" width="14.7109375" customWidth="1"/>
     <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="14.7109375" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="3" t="s">
         <v>45</v>
       </c>
     </row>
@@ -1152,19 +1108,16 @@
         <v>46</v>
       </c>
       <c r="B5" s="4">
-        <v>3822</v>
+        <v>4212</v>
       </c>
       <c r="C5" s="4">
-        <v>6117</v>
+        <v>4678</v>
       </c>
       <c r="D5" s="4">
-        <v>9939</v>
-      </c>
-      <c r="E5" s="4">
-        <v>3871</v>
-      </c>
-      <c r="F5" s="20">
-        <v>0.389</v>
+        <v>8890</v>
+      </c>
+      <c r="E5" s="15">
+        <v>0.47</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1172,19 +1125,16 @@
         <v>47</v>
       </c>
       <c r="B6" s="4">
-        <v>2215</v>
+        <v>2121</v>
       </c>
       <c r="C6" s="4">
-        <v>6808</v>
+        <v>5730</v>
       </c>
       <c r="D6" s="4">
-        <v>9023</v>
-      </c>
-      <c r="E6" s="4">
-        <v>2415</v>
-      </c>
-      <c r="F6" s="20">
-        <v>0.268</v>
+        <v>7851</v>
+      </c>
+      <c r="E6" s="15">
+        <v>0.26</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1192,23 +1142,20 @@
         <v>48</v>
       </c>
       <c r="B7" s="4">
-        <v>359</v>
+        <v>261</v>
       </c>
       <c r="C7" s="4">
-        <v>14210</v>
+        <v>12939</v>
       </c>
       <c r="D7" s="4">
-        <v>14569</v>
-      </c>
-      <c r="E7" s="4">
-        <v>1081</v>
-      </c>
-      <c r="F7" s="20">
-        <v>0.074</v>
+        <v>13200</v>
+      </c>
+      <c r="E7" s="15">
+        <v>0.01</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="16" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1217,7 +1164,7 @@
         <v>50</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>51</v>
@@ -1243,19 +1190,19 @@
         <v>46</v>
       </c>
       <c r="C11" s="4">
-        <v>798</v>
+        <v>1685</v>
       </c>
       <c r="D11" s="4">
-        <v>741</v>
+        <v>1673</v>
       </c>
       <c r="E11" s="4">
-        <v>1176</v>
+        <v>1204</v>
       </c>
       <c r="F11" s="4">
-        <v>1092</v>
-      </c>
-      <c r="G11" s="20">
-        <v>0.929</v>
+        <v>1194</v>
+      </c>
+      <c r="G11" s="17">
+        <v>99.2</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1266,19 +1213,19 @@
         <v>47</v>
       </c>
       <c r="C12" s="4">
-        <v>168</v>
+        <v>955</v>
       </c>
       <c r="D12" s="4">
-        <v>156</v>
+        <v>903</v>
       </c>
       <c r="E12" s="4">
-        <v>546</v>
+        <v>420</v>
       </c>
       <c r="F12" s="4">
-        <v>507</v>
-      </c>
-      <c r="G12" s="20">
-        <v>0.929</v>
+        <v>403</v>
+      </c>
+      <c r="G12" s="17">
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1289,19 +1236,19 @@
         <v>48</v>
       </c>
       <c r="C13" s="4">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="D13" s="4">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="E13" s="4">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="F13" s="4">
-        <v>52</v>
-      </c>
-      <c r="G13" s="20">
-        <v>0.929</v>
+        <v>31</v>
+      </c>
+      <c r="G13" s="17">
+        <v>60.6</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1312,19 +1259,19 @@
         <v>46</v>
       </c>
       <c r="C14" s="4">
-        <v>19</v>
+        <v>911</v>
       </c>
       <c r="D14" s="4">
         <v>1</v>
       </c>
       <c r="E14" s="4">
-        <v>171</v>
+        <v>103</v>
       </c>
       <c r="F14" s="4">
-        <v>9</v>
-      </c>
-      <c r="G14" s="20">
-        <v>0.053</v>
+        <v>0</v>
+      </c>
+      <c r="G14" s="17">
+        <v>0.1</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1335,19 +1282,19 @@
         <v>47</v>
       </c>
       <c r="C15" s="4">
-        <v>114</v>
+        <v>1025</v>
       </c>
       <c r="D15" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E15" s="4">
-        <v>133</v>
+        <v>98</v>
       </c>
       <c r="F15" s="4">
-        <v>7</v>
-      </c>
-      <c r="G15" s="20">
-        <v>0.053</v>
+        <v>0</v>
+      </c>
+      <c r="G15" s="17">
+        <v>0.2</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1358,32 +1305,32 @@
         <v>48</v>
       </c>
       <c r="C16" s="4">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="D16" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="4">
-        <v>209</v>
+        <v>1584</v>
       </c>
       <c r="F16" s="4">
-        <v>11</v>
-      </c>
-      <c r="G16" s="20">
-        <v>0.053</v>
+        <v>0</v>
+      </c>
+      <c r="G16" s="17">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="16" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>58</v>
@@ -1399,56 +1346,61 @@
       <c r="A20" t="s">
         <v>46</v>
       </c>
-      <c r="B20" s="8">
-        <v>38</v>
-      </c>
-      <c r="C20" s="8">
-        <v>91</v>
-      </c>
-      <c r="D20" s="8">
-        <v>98</v>
-      </c>
-      <c r="E20" s="8">
-        <v>67</v>
+      <c r="B20" s="6">
+        <v>47</v>
+      </c>
+      <c r="C20" s="6">
+        <v>74</v>
+      </c>
+      <c r="D20" s="6">
+        <v>65</v>
+      </c>
+      <c r="E20" s="6">
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="8">
-        <v>25</v>
-      </c>
-      <c r="C21" s="8">
-        <v>74</v>
-      </c>
-      <c r="D21" s="8">
-        <v>60</v>
-      </c>
-      <c r="E21" s="8">
-        <v>53</v>
+      <c r="B21" s="6">
+        <v>27</v>
+      </c>
+      <c r="C21" s="6">
+        <v>55</v>
+      </c>
+      <c r="D21" s="6">
+        <v>48</v>
+      </c>
+      <c r="E21" s="6">
+        <v>57</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>48</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="6">
         <v>2</v>
       </c>
-      <c r="C22" s="8">
-        <v>20</v>
-      </c>
-      <c r="D22" s="8">
-        <v>0</v>
-      </c>
-      <c r="E22" s="8">
+      <c r="C22" s="6">
         <v>10</v>
       </c>
+      <c r="D22" s="6">
+        <v>63</v>
+      </c>
+      <c r="E22" s="6">
+        <v>12</v>
+      </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="14" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1475,162 +1427,162 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="32" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" s="4">
-        <v>14395</v>
+        <v>13944</v>
       </c>
       <c r="D5" s="4">
-        <v>13488</v>
+        <v>13378</v>
       </c>
       <c r="E5" s="4">
-        <v>13407</v>
+        <v>13402</v>
       </c>
       <c r="F5" s="4">
-        <v>13344</v>
+        <v>13303</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C6" s="4">
-        <v>14634</v>
+        <v>14401</v>
       </c>
       <c r="D6" s="4">
-        <v>13985</v>
+        <v>13741</v>
       </c>
       <c r="E6" s="4">
-        <v>13922</v>
+        <v>14096</v>
       </c>
       <c r="F6" s="4">
-        <v>13867</v>
+        <v>13944</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C7" s="4">
-        <v>15294</v>
+        <v>15545</v>
       </c>
       <c r="D7" s="4">
-        <v>14515</v>
+        <v>14166</v>
       </c>
       <c r="E7" s="4">
-        <v>14636</v>
+        <v>14328</v>
       </c>
       <c r="F7" s="4">
-        <v>14444</v>
+        <v>14260</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>76</v>
+      <c r="A9" s="16" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" s="4">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D10" s="4">
-        <v>87</v>
+        <v>258</v>
       </c>
       <c r="E10" s="4">
-        <v>194</v>
+        <v>249</v>
       </c>
       <c r="F10" s="4">
-        <v>31</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C11" s="4">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D11" s="4">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="E11" s="4">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="F11" s="4">
-        <v>35</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C12" s="4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D12" s="4">
-        <v>56</v>
+        <v>109</v>
       </c>
       <c r="E12" s="4">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F12" s="4">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>77</v>
+      <c r="A14" s="14" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -1655,12 +1607,12 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.25">
@@ -1674,7 +1626,7 @@
         <v>4</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1682,13 +1634,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
       <c r="D5" s="4">
-        <v>960</v>
+        <v>862</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -1696,13 +1648,13 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" t="s">
-        <v>13</v>
-      </c>
       <c r="D6" s="4">
-        <v>1186</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -1710,13 +1662,13 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
         <v>14</v>
       </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
       <c r="D7" s="4">
-        <v>1077</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -1724,13 +1676,13 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" t="s">
-        <v>17</v>
-      </c>
       <c r="D8" s="4">
-        <v>1020</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -1738,13 +1690,13 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
         <v>18</v>
       </c>
-      <c r="C9" t="s">
-        <v>19</v>
-      </c>
       <c r="D9" s="4">
-        <v>991</v>
+        <v>906</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -1752,13 +1704,13 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
         <v>20</v>
       </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
       <c r="D10" s="4">
-        <v>878</v>
+        <v>854</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -1766,13 +1718,13 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
         <v>22</v>
       </c>
-      <c r="C11" t="s">
-        <v>23</v>
-      </c>
       <c r="D11" s="4">
-        <v>846</v>
+        <v>762</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -1780,13 +1732,13 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
         <v>24</v>
       </c>
-      <c r="C12" t="s">
-        <v>25</v>
-      </c>
       <c r="D12" s="4">
-        <v>504</v>
+        <v>403</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -1794,13 +1746,13 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" t="s">
         <v>26</v>
       </c>
-      <c r="C13" t="s">
-        <v>27</v>
-      </c>
       <c r="D13" s="4">
-        <v>633</v>
+        <v>613</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -1808,13 +1760,13 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
         <v>28</v>
       </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
       <c r="D14" s="4">
-        <v>685</v>
+        <v>642</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -1822,13 +1774,13 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" t="s">
         <v>30</v>
       </c>
-      <c r="C15" t="s">
-        <v>31</v>
-      </c>
       <c r="D15" s="4">
-        <v>386</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -1836,13 +1788,13 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" t="s">
         <v>32</v>
       </c>
-      <c r="C16" t="s">
-        <v>33</v>
-      </c>
       <c r="D16" s="4">
-        <v>607</v>
+        <v>541</v>
       </c>
     </row>
   </sheetData>
